--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8202CC-E821-4CBA-9E66-95C0A7D2CC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C6FAD2-7368-4CD0-B02B-C82BFB780330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -322,6 +322,21 @@
   <si>
     <t>fishStore</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideTable</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>guide.xlsx</t>
+  </si>
+  <si>
+    <t>引导配置</t>
+  </si>
+  <si>
+    <t>guide</t>
   </si>
 </sst>
 </file>
@@ -657,14 +672,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -731,7 +746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -754,7 +769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -783,7 +798,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>35</v>
       </c>
@@ -812,7 +827,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>40</v>
       </c>
@@ -841,7 +856,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
@@ -870,7 +885,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
@@ -899,7 +914,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>55</v>
       </c>
@@ -928,7 +943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>60</v>
       </c>
@@ -957,7 +972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
@@ -986,7 +1001,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>70</v>
       </c>
@@ -1015,7 +1030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>75</v>
       </c>
@@ -1044,7 +1059,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>80</v>
       </c>
@@ -1073,7 +1088,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>85</v>
       </c>
@@ -1102,7 +1117,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>90</v>
       </c>
@@ -1129,6 +1144,35 @@
       </c>
       <c r="K16" s="1" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -1236,6 +1236,51 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>FunctionTable</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>function.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>功能解锁配置</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -1281,6 +1281,141 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>FishRodTable</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>FishRod</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>fishRod.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>鱼钩能力配置</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>fishRod</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>FishTable</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>fish.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>鱼类配置</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>FishBaitTable</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>FishBait</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>fishBait.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>鱼饵效果配置</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>fishBait</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -1416,6 +1416,51 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RandomTable</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RandomProbability</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>random.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -1417,47 +1417,137 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>RandomTable</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>RandomProbability</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>random.xlsx</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ExchangeGroupTable</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ExchangeGroup</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>exchangeGroup.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>兑换组配置</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>exchangeGroup</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ExchangeTable</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>exchange.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>兑换条目配置</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>exchange</t>
         </is>
       </c>
     </row>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -1462,92 +1462,137 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>ExchangeGroupTable</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>ExchangeGroup</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>exchangeGroup.xlsx</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>兑换组配置</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>exchangeGroup</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>ExchangeTable</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>Exchange</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>exchange.xlsx</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>兑换条目配置</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Grow2Table</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Grow2</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>grow2.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>天赋树 Grow2 节点配置</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>grow2</t>
         </is>
       </c>
     </row>
